--- a/research/traditional_assets/database/data/netherlands/netherlands_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_brokerage_investment_banking.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.116</v>
+        <v>0.142</v>
       </c>
       <c r="E2">
-        <v>0.202</v>
+        <v>0.149</v>
       </c>
       <c r="G2">
-        <v>1.213284671532847</v>
+        <v>0.5262881177707676</v>
       </c>
       <c r="H2">
-        <v>1.130656934306569</v>
+        <v>0.4265685243603224</v>
       </c>
       <c r="I2">
-        <v>0.4359124087591241</v>
+        <v>0.3774973711882229</v>
       </c>
       <c r="J2">
-        <v>0.3437727030757988</v>
+        <v>0.2947872730065336</v>
       </c>
       <c r="K2">
-        <v>191.4</v>
+        <v>111.2</v>
       </c>
       <c r="L2">
-        <v>0.2794160583941606</v>
+        <v>0.1948825797406239</v>
       </c>
       <c r="M2">
-        <v>176.61</v>
+        <v>44.29</v>
       </c>
       <c r="N2">
-        <v>0.1107411587659895</v>
+        <v>0.04457528180354267</v>
       </c>
       <c r="O2">
-        <v>0.9227272727272726</v>
+        <v>0.3982913669064748</v>
       </c>
       <c r="P2">
-        <v>176.61</v>
+        <v>44.29</v>
       </c>
       <c r="Q2">
-        <v>0.1107411587659895</v>
+        <v>0.04457528180354267</v>
       </c>
       <c r="R2">
-        <v>0.9227272727272726</v>
+        <v>0.3982913669064748</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -642,67 +642,67 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.2484423676012461</v>
+        <v>0.1823249713067716</v>
       </c>
       <c r="X2">
-        <v>0.0333983830092701</v>
+        <v>0.1115126939931097</v>
       </c>
       <c r="Y2">
-        <v>0.215043984591976</v>
+        <v>0.07081227731366187</v>
       </c>
       <c r="Z2">
-        <v>0.865992414664981</v>
+        <v>0.9120843989769821</v>
       </c>
       <c r="AA2">
-        <v>0.2977045532325185</v>
+        <v>0.2688708727262278</v>
       </c>
       <c r="AB2">
-        <v>0.03329952916587375</v>
+        <v>0.05837353399293474</v>
       </c>
       <c r="AC2">
-        <v>0.2644050240666447</v>
+        <v>0.210497338733293</v>
       </c>
       <c r="AD2">
-        <v>15.7</v>
+        <v>2268.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.7</v>
+        <v>2268.3</v>
       </c>
       <c r="AG2">
-        <v>15.7</v>
+        <v>2268.3</v>
       </c>
       <c r="AH2">
-        <v>0.009748525302701025</v>
+        <v>0.6953922560470892</v>
       </c>
       <c r="AI2">
-        <v>0.02509590792838874</v>
+        <v>0.7989503715966327</v>
       </c>
       <c r="AJ2">
-        <v>0.009748525302701025</v>
+        <v>0.6953922560470892</v>
       </c>
       <c r="AK2">
-        <v>0.02509590792838874</v>
+        <v>0.7989503715966327</v>
       </c>
       <c r="AL2">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="AM2">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="AN2">
-        <v>0.05149229255493604</v>
+        <v>10.22217214961695</v>
       </c>
       <c r="AO2">
-        <v>4.785256410256411</v>
+        <v>3.479806138933764</v>
       </c>
       <c r="AP2">
-        <v>0.05149229255493604</v>
+        <v>10.22217214961695</v>
       </c>
       <c r="AQ2">
-        <v>4.785256410256411</v>
+        <v>3.479806138933764</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.116</v>
+        <v>0.142</v>
       </c>
       <c r="E3">
-        <v>0.202</v>
+        <v>0.149</v>
       </c>
       <c r="G3">
-        <v>1.213284671532847</v>
+        <v>0.5262881177707676</v>
       </c>
       <c r="H3">
-        <v>1.130656934306569</v>
+        <v>0.4265685243603224</v>
       </c>
       <c r="I3">
-        <v>0.4359124087591241</v>
+        <v>0.3774973711882229</v>
       </c>
       <c r="J3">
-        <v>0.3437727030757988</v>
+        <v>0.2947872730065336</v>
       </c>
       <c r="K3">
-        <v>191.4</v>
+        <v>111.2</v>
       </c>
       <c r="L3">
-        <v>0.2794160583941606</v>
+        <v>0.1948825797406239</v>
       </c>
       <c r="M3">
-        <v>176.61</v>
+        <v>44.29</v>
       </c>
       <c r="N3">
-        <v>0.1107411587659895</v>
+        <v>0.04457528180354267</v>
       </c>
       <c r="O3">
-        <v>0.9227272727272726</v>
+        <v>0.3982913669064748</v>
       </c>
       <c r="P3">
-        <v>176.61</v>
+        <v>44.29</v>
       </c>
       <c r="Q3">
-        <v>0.1107411587659895</v>
+        <v>0.04457528180354267</v>
       </c>
       <c r="R3">
-        <v>0.9227272727272726</v>
+        <v>0.3982913669064748</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,67 +776,67 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.2484423676012461</v>
+        <v>0.1823249713067716</v>
       </c>
       <c r="X3">
-        <v>0.0333983830092701</v>
+        <v>0.1115126939931097</v>
       </c>
       <c r="Y3">
-        <v>0.215043984591976</v>
+        <v>0.07081227731366187</v>
       </c>
       <c r="Z3">
-        <v>0.865992414664981</v>
+        <v>0.9120843989769821</v>
       </c>
       <c r="AA3">
-        <v>0.2977045532325185</v>
+        <v>0.2688708727262278</v>
       </c>
       <c r="AB3">
-        <v>0.03329952916587375</v>
+        <v>0.05837353399293474</v>
       </c>
       <c r="AC3">
-        <v>0.2644050240666447</v>
+        <v>0.210497338733293</v>
       </c>
       <c r="AD3">
-        <v>15.7</v>
+        <v>2268.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15.7</v>
+        <v>2268.3</v>
       </c>
       <c r="AG3">
-        <v>15.7</v>
+        <v>2268.3</v>
       </c>
       <c r="AH3">
-        <v>0.009748525302701025</v>
+        <v>0.6953922560470892</v>
       </c>
       <c r="AI3">
-        <v>0.02509590792838874</v>
+        <v>0.7989503715966327</v>
       </c>
       <c r="AJ3">
-        <v>0.009748525302701025</v>
+        <v>0.6953922560470892</v>
       </c>
       <c r="AK3">
-        <v>0.02509590792838874</v>
+        <v>0.7989503715966327</v>
       </c>
       <c r="AL3">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="AM3">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="AN3">
-        <v>0.05149229255493604</v>
+        <v>10.22217214961695</v>
       </c>
       <c r="AO3">
-        <v>4.785256410256411</v>
+        <v>3.479806138933764</v>
       </c>
       <c r="AP3">
-        <v>0.05149229255493604</v>
+        <v>10.22217214961695</v>
       </c>
       <c r="AQ3">
-        <v>4.785256410256411</v>
+        <v>3.479806138933764</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_brokerage_investment_banking.xlsx
@@ -588,46 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.142</v>
+        <v>0.0393</v>
       </c>
       <c r="E2">
-        <v>0.149</v>
+        <v>-0.162</v>
+      </c>
+      <c r="F2">
+        <v>-0.19</v>
       </c>
       <c r="G2">
-        <v>0.5262881177707676</v>
+        <v>0.6055983908816628</v>
       </c>
       <c r="H2">
-        <v>0.4265685243603224</v>
+        <v>0.4894401609118337</v>
       </c>
       <c r="I2">
-        <v>0.3774973711882229</v>
+        <v>0.3147837747234328</v>
       </c>
       <c r="J2">
-        <v>0.2947872730065336</v>
+        <v>0.2479515411452165</v>
       </c>
       <c r="K2">
-        <v>111.2</v>
+        <v>62.7</v>
       </c>
       <c r="L2">
-        <v>0.1948825797406239</v>
+        <v>0.1050955414012739</v>
       </c>
       <c r="M2">
-        <v>44.29</v>
+        <v>50.22799999999999</v>
       </c>
       <c r="N2">
-        <v>0.04457528180354267</v>
+        <v>0.0584454270421224</v>
       </c>
       <c r="O2">
-        <v>0.3982913669064748</v>
+        <v>0.8010845295055821</v>
       </c>
       <c r="P2">
-        <v>44.29</v>
+        <v>50.22799999999999</v>
       </c>
       <c r="Q2">
-        <v>0.04457528180354267</v>
+        <v>0.0584454270421224</v>
       </c>
       <c r="R2">
-        <v>0.3982913669064748</v>
+        <v>0.8010845295055821</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -642,67 +645,67 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.1823249713067716</v>
+        <v>0.1098458304134548</v>
       </c>
       <c r="X2">
-        <v>0.1115126939931097</v>
+        <v>0.09856829667050424</v>
       </c>
       <c r="Y2">
-        <v>0.07081227731366187</v>
+        <v>0.01127753374295058</v>
       </c>
       <c r="Z2">
-        <v>0.9120843989769821</v>
+        <v>0.210137015251312</v>
       </c>
       <c r="AA2">
-        <v>0.2688708727262278</v>
+        <v>0.05210379678321869</v>
       </c>
       <c r="AB2">
-        <v>0.05837353399293474</v>
+        <v>0.04902407079272973</v>
       </c>
       <c r="AC2">
-        <v>0.210497338733293</v>
+        <v>0.00307972599048896</v>
       </c>
       <c r="AD2">
-        <v>2268.3</v>
+        <v>2729</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2268.3</v>
+        <v>2729</v>
       </c>
       <c r="AG2">
-        <v>2268.3</v>
+        <v>2729</v>
       </c>
       <c r="AH2">
-        <v>0.6953922560470892</v>
+        <v>0.7605060751309776</v>
       </c>
       <c r="AI2">
-        <v>0.7989503715966327</v>
+        <v>0.8148214498984833</v>
       </c>
       <c r="AJ2">
-        <v>0.6953922560470892</v>
+        <v>0.7605060751309776</v>
       </c>
       <c r="AK2">
-        <v>0.7989503715966327</v>
+        <v>0.8148214498984833</v>
       </c>
       <c r="AL2">
-        <v>61.9</v>
+        <v>109.6</v>
       </c>
       <c r="AM2">
-        <v>61.9</v>
+        <v>109.6</v>
       </c>
       <c r="AN2">
-        <v>10.22217214961695</v>
+        <v>13.93769152196118</v>
       </c>
       <c r="AO2">
-        <v>3.479806138933764</v>
+        <v>1.713503649635037</v>
       </c>
       <c r="AP2">
-        <v>10.22217214961695</v>
+        <v>13.93769152196118</v>
       </c>
       <c r="AQ2">
-        <v>3.479806138933764</v>
+        <v>1.713503649635037</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Flow Traders N.V. (ENXTAM:FLOW)</t>
+          <t>Flow Traders Ltd. (ENXTAM:FLOW)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.142</v>
+        <v>0.0393</v>
       </c>
       <c r="E3">
-        <v>0.149</v>
+        <v>-0.162</v>
+      </c>
+      <c r="F3">
+        <v>-0.19</v>
       </c>
       <c r="G3">
-        <v>0.5262881177707676</v>
+        <v>0.6055983908816628</v>
       </c>
       <c r="H3">
-        <v>0.4265685243603224</v>
+        <v>0.4894401609118337</v>
       </c>
       <c r="I3">
-        <v>0.3774973711882229</v>
+        <v>0.3147837747234328</v>
       </c>
       <c r="J3">
-        <v>0.2947872730065336</v>
+        <v>0.2479515411452165</v>
       </c>
       <c r="K3">
-        <v>111.2</v>
+        <v>62.7</v>
       </c>
       <c r="L3">
-        <v>0.1948825797406239</v>
+        <v>0.1050955414012739</v>
       </c>
       <c r="M3">
-        <v>44.29</v>
+        <v>50.22799999999999</v>
       </c>
       <c r="N3">
-        <v>0.04457528180354267</v>
+        <v>0.0584454270421224</v>
       </c>
       <c r="O3">
-        <v>0.3982913669064748</v>
+        <v>0.8010845295055821</v>
       </c>
       <c r="P3">
-        <v>44.29</v>
+        <v>50.22799999999999</v>
       </c>
       <c r="Q3">
-        <v>0.04457528180354267</v>
+        <v>0.0584454270421224</v>
       </c>
       <c r="R3">
-        <v>0.3982913669064748</v>
+        <v>0.8010845295055821</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,67 +782,67 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1823249713067716</v>
+        <v>0.1098458304134548</v>
       </c>
       <c r="X3">
-        <v>0.1115126939931097</v>
+        <v>0.09856829667050424</v>
       </c>
       <c r="Y3">
-        <v>0.07081227731366187</v>
+        <v>0.01127753374295058</v>
       </c>
       <c r="Z3">
-        <v>0.9120843989769821</v>
+        <v>0.210137015251312</v>
       </c>
       <c r="AA3">
-        <v>0.2688708727262278</v>
+        <v>0.05210379678321869</v>
       </c>
       <c r="AB3">
-        <v>0.05837353399293474</v>
+        <v>0.04902407079272973</v>
       </c>
       <c r="AC3">
-        <v>0.210497338733293</v>
+        <v>0.00307972599048896</v>
       </c>
       <c r="AD3">
-        <v>2268.3</v>
+        <v>2729</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2268.3</v>
+        <v>2729</v>
       </c>
       <c r="AG3">
-        <v>2268.3</v>
+        <v>2729</v>
       </c>
       <c r="AH3">
-        <v>0.6953922560470892</v>
+        <v>0.7605060751309776</v>
       </c>
       <c r="AI3">
-        <v>0.7989503715966327</v>
+        <v>0.8148214498984833</v>
       </c>
       <c r="AJ3">
-        <v>0.6953922560470892</v>
+        <v>0.7605060751309776</v>
       </c>
       <c r="AK3">
-        <v>0.7989503715966327</v>
+        <v>0.8148214498984833</v>
       </c>
       <c r="AL3">
-        <v>61.9</v>
+        <v>109.6</v>
       </c>
       <c r="AM3">
-        <v>61.9</v>
+        <v>109.6</v>
       </c>
       <c r="AN3">
-        <v>10.22217214961695</v>
+        <v>13.93769152196118</v>
       </c>
       <c r="AO3">
-        <v>3.479806138933764</v>
+        <v>1.713503649635037</v>
       </c>
       <c r="AP3">
-        <v>10.22217214961695</v>
+        <v>13.93769152196118</v>
       </c>
       <c r="AQ3">
-        <v>3.479806138933764</v>
+        <v>1.713503649635037</v>
       </c>
     </row>
   </sheetData>
